--- a/MobileSuitDatabase/docs/詳細設計/詳細情報.xlsx
+++ b/MobileSuitDatabase/docs/詳細設計/詳細情報.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mk26s\git\MobileSuitDatabase\MobileSuitDatabase\docs\詳細設計\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97DF981B-7E40-4E4B-ABAC-E21CE7B4FCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06E59A0-7CBA-4BC7-B099-50C6A1DF1A31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{B78654B8-3228-4DDE-84FC-2FEFE59689A6}"/>
   </bookViews>
@@ -3915,15 +3915,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
+      <xdr:colOff>144780</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>472440</xdr:colOff>
+      <xdr:colOff>586740</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3938,8 +3938,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8892540" y="1104900"/>
-          <a:ext cx="1638300" cy="457200"/>
+          <a:off x="8862060" y="1066800"/>
+          <a:ext cx="1783080" cy="571500"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3975,13 +3975,237 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
-            <a:t>List&lt;MobileSuitArmdModel&gt;</a:t>
+            <a:t>List&lt;MobileSuitEquipmentModel&gt;</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900" baseline="0"/>
-            <a:t> findMobileSuitArms(String)</a:t>
+            <a:t> findMobileSuitEquipments(String)</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="テキスト ボックス 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DB0F592-90A6-4F17-8A0C-B4D1F4D2A90A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10957560" y="815340"/>
+          <a:ext cx="1638300" cy="457200"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+            <a:t>MobileSuitEntity</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900" baseline="0"/>
+            <a:t> findMobileSuitById(String)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="テキスト ボックス 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2D8E8732-D3F0-4207-9AEC-0890D26ADF06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10881360" y="1348740"/>
+          <a:ext cx="1783080" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+            <a:t>List&lt;MobileSuitEquipmentEntity&gt;</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900" baseline="0"/>
+            <a:t> findMobileSuitEquipmentsById(String)</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>129540</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="テキスト ボックス 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{734593FB-A1F1-44F8-A98A-D49AAE79D22C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3108960" y="3939540"/>
+          <a:ext cx="1082040" cy="236220"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="900"/>
+            <a:t>GET </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="900"/>
+            <a:t>レスポンス</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
